--- a/Saves/130/План-график_гр130_Заяц_Иван_Спанович_четная_Песина.xlsx
+++ b/Saves/130/План-график_гр130_Заяц_Иван_Спанович_четная_Песина.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,11 @@
     </font>
     <font>
       <name val="Arial Cyr"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial Cyr"/>
+      <b val="1"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -72,13 +77,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -87,7 +98,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -96,6 +107,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,41 +475,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM23"/>
+  <dimension ref="A1:AG23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="4" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="4" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
-    <col width="4" customWidth="1" min="9" max="9"/>
-    <col width="4" customWidth="1" min="10" max="10"/>
-    <col width="4" customWidth="1" min="11" max="11"/>
-    <col width="4" customWidth="1" min="12" max="12"/>
-    <col width="4" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
-    <col width="4" customWidth="1" min="18" max="18"/>
-    <col width="4" customWidth="1" min="19" max="19"/>
-    <col width="4" customWidth="1" min="20" max="20"/>
-    <col width="4" customWidth="1" min="21" max="21"/>
-    <col width="4" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
-    <col width="4" customWidth="1" min="27" max="27"/>
-    <col width="4" customWidth="1" min="28" max="28"/>
-    <col width="4" customWidth="1" min="29" max="29"/>
-    <col width="4" customWidth="1" min="30" max="30"/>
-    <col width="4" customWidth="1" min="31" max="31"/>
-    <col width="4" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="3.5" customWidth="1" min="2" max="2"/>
+    <col width="3.5" customWidth="1" min="3" max="3"/>
+    <col width="3.5" customWidth="1" min="4" max="4"/>
+    <col width="3.5" customWidth="1" min="5" max="5"/>
+    <col width="3.5" customWidth="1" min="6" max="6"/>
+    <col width="3.5" customWidth="1" min="7" max="7"/>
+    <col width="3.5" customWidth="1" min="8" max="8"/>
+    <col width="3.5" customWidth="1" min="9" max="9"/>
+    <col width="3.5" customWidth="1" min="10" max="10"/>
+    <col width="3.5" customWidth="1" min="11" max="11"/>
+    <col width="3.5" customWidth="1" min="12" max="12"/>
+    <col width="3.5" customWidth="1" min="13" max="13"/>
+    <col width="3.5" customWidth="1" min="14" max="14"/>
+    <col width="3.5" customWidth="1" min="15" max="15"/>
+    <col width="3.5" customWidth="1" min="16" max="16"/>
+    <col width="3.5" customWidth="1" min="17" max="17"/>
+    <col width="3.5" customWidth="1" min="18" max="18"/>
+    <col width="3.5" customWidth="1" min="19" max="19"/>
+    <col width="3.5" customWidth="1" min="20" max="20"/>
+    <col width="3.5" customWidth="1" min="21" max="21"/>
+    <col width="3.5" customWidth="1" min="22" max="22"/>
+    <col width="3.5" customWidth="1" min="23" max="23"/>
+    <col width="3.5" customWidth="1" min="24" max="24"/>
+    <col width="3.5" customWidth="1" min="25" max="25"/>
+    <col width="3.5" customWidth="1" min="26" max="26"/>
+    <col width="3.5" customWidth="1" min="27" max="27"/>
+    <col width="3.5" customWidth="1" min="28" max="28"/>
+    <col width="3.5" customWidth="1" min="29" max="29"/>
+    <col width="3.5" customWidth="1" min="30" max="30"/>
+    <col width="3.5" customWidth="1" min="31" max="31"/>
+    <col width="3.5" customWidth="1" min="32" max="32"/>
     <col width="8" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
@@ -505,42 +519,42 @@
           <t>ООО "Своя автошкола"</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>"УТВЕРЖДАЮ"</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Директор</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="AB3" s="1" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>_______________ В.В. Евтушков</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>"05" июня 2026 года</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>План-график выполнения единой программы переподготовки водителей механических транспортных средств категории «В» на право управления составами транспортных средств категории «ВЕ»</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>учебная группа № 130</t>
         </is>
@@ -552,7 +566,7 @@
           <t>Преподаватель</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Заяц Иван Спанович</t>
         </is>
@@ -564,7 +578,7 @@
           <t>Дни</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Чётные дни</t>
         </is>
@@ -576,7 +590,7 @@
           <t>Кроме</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>30.06.2026, 14.08.2026, 28.08.2026</t>
         </is>
@@ -588,7 +602,7 @@
           <t>Дополнительные дни</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>05.08.2026, 07.08.2026, 13.08.2026</t>
         </is>
@@ -600,7 +614,7 @@
           <t>Время</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>09:00 - 17:00</t>
         </is>
@@ -612,481 +626,484 @@
           <t>Место</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Песина</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Дата/Тема</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Июнь 2026</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>Июль 2026</t>
         </is>
       </c>
-      <c r="U17" s="5" t="inlineStr">
+      <c r="U17" s="7" t="inlineStr">
         <is>
           <t>Август 2026</t>
         </is>
       </c>
-      <c r="AF17" s="5" t="inlineStr">
+      <c r="AF17" s="7" t="inlineStr">
         <is>
           <t>Сентябрь 2026</t>
         </is>
       </c>
-      <c r="AG17" s="5" t="inlineStr">
+      <c r="AG17" s="7" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="D18" s="6" t="n">
+      <c r="C18" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="K18" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="L18" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="M18" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="N18" s="6" t="n">
+      <c r="M18" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N18" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="O18" s="6" t="n">
+      <c r="O18" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="P18" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="Q18" s="6" t="n">
+      <c r="Q18" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="R18" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="S18" s="6" t="n">
+      <c r="S18" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="T18" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="U18" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="V18" s="6" t="n">
+      <c r="U18" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V18" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="W18" s="6" t="n">
+      <c r="W18" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="X18" s="6" t="n">
+      <c r="X18" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="Y18" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z18" s="6" t="n">
+      <c r="Y18" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z18" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="AA18" s="6" t="n">
+      <c r="AA18" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="AB18" s="6" t="n">
+      <c r="AB18" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="AC18" s="6" t="n">
+      <c r="AC18" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="AD18" s="6" t="n">
+      <c r="AD18" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="AE18" s="6" t="n">
+      <c r="AE18" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="AF18" s="6" t="n">
+      <c r="AF18" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AG18" s="7" t="inlineStr"/>
+      <c r="AG18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C19" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" s="9" t="n">
+      <c r="C19" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="H19" s="9" t="n">
+      <c r="H19" s="11" t="n">
         <v>10.5</v>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="I19" s="11" t="n">
         <v>8.5</v>
       </c>
-      <c r="J19" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="K19" s="9" t="n">
+      <c r="J19" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K19" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="M19" s="9" t="n">
+      <c r="M19" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="N19" s="9" t="n">
+      <c r="N19" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="O19" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P19" s="9" t="n">
+      <c r="O19" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P19" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="Q19" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="R19" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="S19" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" s="9" t="n">
+      <c r="Q19" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S19" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="U19" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="V19" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="W19" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="X19" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y19" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z19" s="9" t="n">
+      <c r="U19" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V19" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="W19" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="X19" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y19" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z19" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="AA19" s="9" t="n">
+      <c r="AA19" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="AB19" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC19" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD19" s="9" t="n">
+      <c r="AB19" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC19" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD19" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="AE19" s="9" t="n">
+      <c r="AE19" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="AF19" s="9" t="n">
+      <c r="AF19" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="AG19" s="7" t="inlineStr"/>
+      <c r="AG19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>ОУТС И БД кат С</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C20" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" s="6" t="n">
+      <c r="C20" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="H20" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I20" s="6" t="n">
+      <c r="H20" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="J20" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K20" s="6" t="inlineStr"/>
-      <c r="L20" s="6" t="inlineStr"/>
-      <c r="M20" s="6" t="inlineStr"/>
-      <c r="N20" s="6" t="inlineStr"/>
-      <c r="O20" s="6" t="inlineStr"/>
-      <c r="P20" s="6" t="inlineStr"/>
-      <c r="Q20" s="6" t="inlineStr"/>
-      <c r="R20" s="6" t="inlineStr"/>
-      <c r="S20" s="6" t="inlineStr"/>
-      <c r="T20" s="6" t="inlineStr"/>
-      <c r="U20" s="6" t="inlineStr"/>
-      <c r="V20" s="6" t="inlineStr"/>
-      <c r="W20" s="6" t="inlineStr"/>
-      <c r="X20" s="6" t="inlineStr"/>
-      <c r="Y20" s="6" t="inlineStr"/>
-      <c r="Z20" s="6" t="inlineStr"/>
-      <c r="AA20" s="6" t="inlineStr"/>
-      <c r="AB20" s="6" t="inlineStr"/>
-      <c r="AC20" s="6" t="inlineStr"/>
-      <c r="AD20" s="6" t="inlineStr"/>
-      <c r="AE20" s="6" t="inlineStr"/>
-      <c r="AF20" s="6" t="inlineStr"/>
-      <c r="AG20" s="9" t="n">
+      <c r="J20" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" s="13" t="inlineStr"/>
+      <c r="L20" s="13" t="inlineStr"/>
+      <c r="M20" s="13" t="inlineStr"/>
+      <c r="N20" s="13" t="inlineStr"/>
+      <c r="O20" s="13" t="inlineStr"/>
+      <c r="P20" s="13" t="inlineStr"/>
+      <c r="Q20" s="13" t="inlineStr"/>
+      <c r="R20" s="13" t="inlineStr"/>
+      <c r="S20" s="13" t="inlineStr"/>
+      <c r="T20" s="13" t="inlineStr"/>
+      <c r="U20" s="13" t="inlineStr"/>
+      <c r="V20" s="13" t="inlineStr"/>
+      <c r="W20" s="13" t="inlineStr"/>
+      <c r="X20" s="13" t="inlineStr"/>
+      <c r="Y20" s="13" t="inlineStr"/>
+      <c r="Z20" s="13" t="inlineStr"/>
+      <c r="AA20" s="13" t="inlineStr"/>
+      <c r="AB20" s="13" t="inlineStr"/>
+      <c r="AC20" s="13" t="inlineStr"/>
+      <c r="AD20" s="13" t="inlineStr"/>
+      <c r="AE20" s="13" t="inlineStr"/>
+      <c r="AF20" s="13" t="inlineStr"/>
+      <c r="AG20" s="11" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Медицина</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr"/>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
-      <c r="L21" s="6" t="inlineStr"/>
-      <c r="M21" s="6" t="inlineStr"/>
-      <c r="N21" s="6" t="inlineStr"/>
-      <c r="O21" s="6" t="inlineStr"/>
-      <c r="P21" s="6" t="inlineStr"/>
-      <c r="Q21" s="6" t="inlineStr"/>
-      <c r="R21" s="6" t="inlineStr"/>
-      <c r="S21" s="6" t="inlineStr"/>
-      <c r="T21" s="6" t="inlineStr"/>
-      <c r="U21" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="V21" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="W21" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="X21" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y21" s="6" t="inlineStr"/>
-      <c r="Z21" s="6" t="inlineStr"/>
-      <c r="AA21" s="6" t="inlineStr"/>
-      <c r="AB21" s="6" t="inlineStr"/>
-      <c r="AC21" s="6" t="inlineStr"/>
-      <c r="AD21" s="6" t="inlineStr"/>
-      <c r="AE21" s="6" t="inlineStr"/>
-      <c r="AF21" s="6" t="inlineStr"/>
-      <c r="AG21" s="9" t="n">
+      <c r="B21" s="13" t="inlineStr"/>
+      <c r="C21" s="13" t="inlineStr"/>
+      <c r="D21" s="13" t="inlineStr"/>
+      <c r="E21" s="13" t="inlineStr"/>
+      <c r="F21" s="13" t="inlineStr"/>
+      <c r="G21" s="13" t="inlineStr"/>
+      <c r="H21" s="13" t="inlineStr"/>
+      <c r="I21" s="13" t="inlineStr"/>
+      <c r="J21" s="13" t="inlineStr"/>
+      <c r="K21" s="13" t="inlineStr"/>
+      <c r="L21" s="13" t="inlineStr"/>
+      <c r="M21" s="13" t="inlineStr"/>
+      <c r="N21" s="13" t="inlineStr"/>
+      <c r="O21" s="13" t="inlineStr"/>
+      <c r="P21" s="13" t="inlineStr"/>
+      <c r="Q21" s="13" t="inlineStr"/>
+      <c r="R21" s="13" t="inlineStr"/>
+      <c r="S21" s="13" t="inlineStr"/>
+      <c r="T21" s="13" t="inlineStr"/>
+      <c r="U21" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="V21" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="W21" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="X21" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="13" t="inlineStr"/>
+      <c r="Z21" s="13" t="inlineStr"/>
+      <c r="AA21" s="13" t="inlineStr"/>
+      <c r="AB21" s="13" t="inlineStr"/>
+      <c r="AC21" s="13" t="inlineStr"/>
+      <c r="AD21" s="13" t="inlineStr"/>
+      <c r="AE21" s="13" t="inlineStr"/>
+      <c r="AF21" s="13" t="inlineStr"/>
+      <c r="AG21" s="11" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>У и ЭА кат. "С"</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr"/>
-      <c r="C22" s="6" t="inlineStr"/>
-      <c r="D22" s="6" t="inlineStr"/>
-      <c r="E22" s="6" t="inlineStr"/>
-      <c r="F22" s="6" t="inlineStr"/>
-      <c r="G22" s="6" t="inlineStr"/>
-      <c r="H22" s="6" t="inlineStr"/>
-      <c r="I22" s="6" t="inlineStr"/>
-      <c r="J22" s="6" t="inlineStr"/>
-      <c r="K22" s="6" t="n">
+      <c r="B22" s="13" t="inlineStr"/>
+      <c r="C22" s="13" t="inlineStr"/>
+      <c r="D22" s="13" t="inlineStr"/>
+      <c r="E22" s="13" t="inlineStr"/>
+      <c r="F22" s="13" t="inlineStr"/>
+      <c r="G22" s="13" t="inlineStr"/>
+      <c r="H22" s="13" t="inlineStr"/>
+      <c r="I22" s="13" t="inlineStr"/>
+      <c r="J22" s="13" t="inlineStr"/>
+      <c r="K22" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="L22" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="M22" s="6" t="n">
+      <c r="M22" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="N22" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="O22" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="S22" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T22" s="6" t="n">
+      <c r="O22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="U22" s="6" t="inlineStr"/>
-      <c r="V22" s="6" t="inlineStr"/>
-      <c r="W22" s="6" t="inlineStr"/>
-      <c r="X22" s="6" t="inlineStr"/>
-      <c r="Y22" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z22" s="6" t="n">
+      <c r="U22" s="13" t="inlineStr"/>
+      <c r="V22" s="13" t="inlineStr"/>
+      <c r="W22" s="13" t="inlineStr"/>
+      <c r="X22" s="13" t="inlineStr"/>
+      <c r="Y22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z22" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="AA22" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB22" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC22" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD22" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE22" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF22" s="6" t="inlineStr"/>
-      <c r="AG22" s="9" t="n">
+      <c r="AA22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF22" s="13" t="inlineStr"/>
+      <c r="AG22" s="11" t="n">
         <v>72</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Экзамен</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr"/>
-      <c r="C23" s="6" t="inlineStr"/>
-      <c r="D23" s="6" t="inlineStr"/>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr"/>
-      <c r="G23" s="6" t="inlineStr"/>
-      <c r="H23" s="6" t="inlineStr"/>
-      <c r="I23" s="6" t="inlineStr"/>
-      <c r="J23" s="6" t="inlineStr"/>
-      <c r="K23" s="6" t="inlineStr"/>
-      <c r="L23" s="6" t="inlineStr"/>
-      <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="6" t="inlineStr"/>
-      <c r="O23" s="6" t="inlineStr"/>
-      <c r="P23" s="6" t="inlineStr"/>
-      <c r="Q23" s="6" t="inlineStr"/>
-      <c r="R23" s="6" t="inlineStr"/>
-      <c r="S23" s="6" t="inlineStr"/>
-      <c r="T23" s="6" t="inlineStr"/>
-      <c r="U23" s="6" t="inlineStr"/>
-      <c r="V23" s="6" t="inlineStr"/>
-      <c r="W23" s="6" t="inlineStr"/>
-      <c r="X23" s="6" t="inlineStr"/>
-      <c r="Y23" s="6" t="inlineStr"/>
-      <c r="Z23" s="6" t="inlineStr"/>
-      <c r="AA23" s="6" t="inlineStr"/>
-      <c r="AB23" s="6" t="inlineStr"/>
-      <c r="AC23" s="6" t="inlineStr"/>
-      <c r="AD23" s="6" t="inlineStr"/>
-      <c r="AE23" s="6" t="inlineStr"/>
-      <c r="AF23" s="6" t="n">
+      <c r="B23" s="13" t="inlineStr"/>
+      <c r="C23" s="13" t="inlineStr"/>
+      <c r="D23" s="13" t="inlineStr"/>
+      <c r="E23" s="13" t="inlineStr"/>
+      <c r="F23" s="13" t="inlineStr"/>
+      <c r="G23" s="13" t="inlineStr"/>
+      <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr"/>
+      <c r="J23" s="13" t="inlineStr"/>
+      <c r="K23" s="13" t="inlineStr"/>
+      <c r="L23" s="13" t="inlineStr"/>
+      <c r="M23" s="13" t="inlineStr"/>
+      <c r="N23" s="13" t="inlineStr"/>
+      <c r="O23" s="13" t="inlineStr"/>
+      <c r="P23" s="13" t="inlineStr"/>
+      <c r="Q23" s="13" t="inlineStr"/>
+      <c r="R23" s="13" t="inlineStr"/>
+      <c r="S23" s="13" t="inlineStr"/>
+      <c r="T23" s="13" t="inlineStr"/>
+      <c r="U23" s="13" t="inlineStr"/>
+      <c r="V23" s="13" t="inlineStr"/>
+      <c r="W23" s="13" t="inlineStr"/>
+      <c r="X23" s="13" t="inlineStr"/>
+      <c r="Y23" s="13" t="inlineStr"/>
+      <c r="Z23" s="13" t="inlineStr"/>
+      <c r="AA23" s="13" t="inlineStr"/>
+      <c r="AB23" s="13" t="inlineStr"/>
+      <c r="AC23" s="13" t="inlineStr"/>
+      <c r="AD23" s="13" t="inlineStr"/>
+      <c r="AE23" s="13" t="inlineStr"/>
+      <c r="AF23" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="AG23" s="9" t="n">
+      <c r="AG23" s="11" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B15:AM15"/>
-    <mergeCell ref="B10:AM10"/>
-    <mergeCell ref="B11:AM11"/>
-    <mergeCell ref="AB1:AM1"/>
+  <mergeCells count="16">
+    <mergeCell ref="B10:AG10"/>
     <mergeCell ref="J17:T17"/>
-    <mergeCell ref="A8:AM8"/>
-    <mergeCell ref="A6:AM6"/>
+    <mergeCell ref="Z4:AG4"/>
+    <mergeCell ref="A8:AG8"/>
+    <mergeCell ref="U1:AG1"/>
+    <mergeCell ref="A6:AG6"/>
+    <mergeCell ref="B14:AG14"/>
     <mergeCell ref="AF17"/>
     <mergeCell ref="U17:AE17"/>
-    <mergeCell ref="B14:AM14"/>
-    <mergeCell ref="B13:AM13"/>
-    <mergeCell ref="B12:AM12"/>
+    <mergeCell ref="B12:AG12"/>
+    <mergeCell ref="B13:AG13"/>
+    <mergeCell ref="U3:AG3"/>
+    <mergeCell ref="B15:AG15"/>
+    <mergeCell ref="B11:AG11"/>
+    <mergeCell ref="U2:AG2"/>
     <mergeCell ref="B17:I17"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>

--- a/Saves/130/План-график_гр130_Заяц_Иван_Спанович_четная_Песина.xlsx
+++ b/Saves/130/План-график_гр130_Заяц_Иван_Спанович_четная_Песина.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG23"/>
+  <dimension ref="A1:AF23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -509,8 +509,7 @@
     <col width="3.5" customWidth="1" min="29" max="29"/>
     <col width="3.5" customWidth="1" min="30" max="30"/>
     <col width="3.5" customWidth="1" min="31" max="31"/>
-    <col width="3.5" customWidth="1" min="32" max="32"/>
-    <col width="8" customWidth="1" min="33" max="33"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,28 +518,28 @@
           <t>ООО "Своя автошкола"</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>"УТВЕРЖДАЮ"</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="U2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>Директор</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="U3" s="2" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>_______________ В.В. Евтушков</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="Z4" s="3" t="inlineStr">
+    <row r="4">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>"05" июня 2026 года</t>
         </is>
@@ -592,7 +591,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>30.06.2026, 14.08.2026, 28.08.2026</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -604,7 +603,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>05.08.2026, 07.08.2026, 13.08.2026</t>
+          <t>05.08.2026, 07.08.2026</t>
         </is>
       </c>
     </row>
@@ -653,12 +652,12 @@
           <t>Август 2026</t>
         </is>
       </c>
+      <c r="AE17" s="7" t="inlineStr">
+        <is>
+          <t>Сентябрь 2026</t>
+        </is>
+      </c>
       <c r="AF17" s="7" t="inlineStr">
-        <is>
-          <t>Сентябрь 2026</t>
-        </is>
-      </c>
-      <c r="AG17" s="7" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -741,24 +740,21 @@
         <v>12</v>
       </c>
       <c r="AA18" s="8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AB18" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AC18" s="8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AD18" s="8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE18" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF18" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="AG18" s="9" t="inlineStr"/>
+      <c r="AF18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -842,24 +838,21 @@
         <v>8</v>
       </c>
       <c r="AA19" s="11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AB19" s="11" t="n">
         <v>10</v>
       </c>
       <c r="AC19" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD19" s="11" t="n">
         <v>8</v>
       </c>
       <c r="AE19" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF19" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="AG19" s="9" t="inlineStr"/>
+      <c r="AF19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -915,8 +908,7 @@
       <c r="AC20" s="13" t="inlineStr"/>
       <c r="AD20" s="13" t="inlineStr"/>
       <c r="AE20" s="13" t="inlineStr"/>
-      <c r="AF20" s="13" t="inlineStr"/>
-      <c r="AG20" s="11" t="n">
+      <c r="AF20" s="11" t="n">
         <v>38</v>
       </c>
     </row>
@@ -964,8 +956,7 @@
       <c r="AC21" s="13" t="inlineStr"/>
       <c r="AD21" s="13" t="inlineStr"/>
       <c r="AE21" s="13" t="inlineStr"/>
-      <c r="AF21" s="13" t="inlineStr"/>
-      <c r="AG21" s="11" t="n">
+      <c r="AF21" s="11" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1036,12 +1027,9 @@
       <c r="AD22" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="AE22" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF22" s="13" t="inlineStr"/>
-      <c r="AG22" s="11" t="n">
-        <v>72</v>
+      <c r="AE22" s="13" t="inlineStr"/>
+      <c r="AF22" s="11" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="23">
@@ -1079,31 +1067,30 @@
       <c r="AB23" s="13" t="inlineStr"/>
       <c r="AC23" s="13" t="inlineStr"/>
       <c r="AD23" s="13" t="inlineStr"/>
-      <c r="AE23" s="13" t="inlineStr"/>
-      <c r="AF23" s="13" t="n">
+      <c r="AE23" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="AG23" s="11" t="n">
+      <c r="AF23" s="11" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B10:AG10"/>
+    <mergeCell ref="B12:AF12"/>
     <mergeCell ref="J17:T17"/>
-    <mergeCell ref="Z4:AG4"/>
-    <mergeCell ref="A8:AG8"/>
-    <mergeCell ref="U1:AG1"/>
-    <mergeCell ref="A6:AG6"/>
-    <mergeCell ref="B14:AG14"/>
-    <mergeCell ref="AF17"/>
-    <mergeCell ref="U17:AE17"/>
-    <mergeCell ref="B12:AG12"/>
-    <mergeCell ref="B13:AG13"/>
-    <mergeCell ref="U3:AG3"/>
-    <mergeCell ref="B15:AG15"/>
-    <mergeCell ref="B11:AG11"/>
-    <mergeCell ref="U2:AG2"/>
+    <mergeCell ref="T1:AF1"/>
+    <mergeCell ref="Y4:AF4"/>
+    <mergeCell ref="B15:AF15"/>
+    <mergeCell ref="B10:AF10"/>
+    <mergeCell ref="B11:AF11"/>
+    <mergeCell ref="AE17"/>
+    <mergeCell ref="A8:AF8"/>
+    <mergeCell ref="A6:AF6"/>
+    <mergeCell ref="T3:AF3"/>
+    <mergeCell ref="B14:AF14"/>
+    <mergeCell ref="U17:AD17"/>
+    <mergeCell ref="B13:AF13"/>
+    <mergeCell ref="T2:AF2"/>
     <mergeCell ref="B17:I17"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>

--- a/Saves/130/План-график_гр130_Заяц_Иван_Спанович_четная_Песина.xlsx
+++ b/Saves/130/План-график_гр130_Заяц_Иван_Спанович_четная_Песина.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF23"/>
+  <dimension ref="A1:AF25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>План-график выполнения единой программы переподготовки водителей механических транспортных средств категории «В» на право управления составами транспортных средств категории «ВЕ»</t>
+          <t>План-график выполнения единой программы подготовки водителей МТС категории "B"</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.08.2026, 20.08.2026, 28.08.2026</t>
         </is>
       </c>
     </row>
@@ -642,12 +642,12 @@
           <t>Июнь 2026</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>Июль 2026</t>
         </is>
       </c>
-      <c r="U17" s="7" t="inlineStr">
+      <c r="V17" s="7" t="inlineStr">
         <is>
           <t>Август 2026</t>
         </is>
@@ -689,61 +689,61 @@
         <v>26</v>
       </c>
       <c r="J18" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="K18" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="K18" s="8" t="n">
-        <v>6</v>
-      </c>
       <c r="L18" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M18" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="N18" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="N18" s="8" t="n">
+      <c r="O18" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="O18" s="8" t="n">
+      <c r="P18" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="P18" s="8" t="n">
+      <c r="Q18" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="Q18" s="8" t="n">
+      <c r="R18" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="S18" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="S18" s="8" t="n">
+      <c r="T18" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="T18" s="8" t="n">
+      <c r="U18" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="U18" s="8" t="n">
-        <v>4</v>
-      </c>
       <c r="V18" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="W18" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="W18" s="8" t="n">
-        <v>6</v>
-      </c>
       <c r="X18" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y18" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="Y18" s="8" t="n">
+      <c r="Z18" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="Z18" s="8" t="n">
+      <c r="AA18" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="AA18" s="8" t="n">
+      <c r="AB18" s="8" t="n">
         <v>18</v>
-      </c>
-      <c r="AB18" s="8" t="n">
-        <v>20</v>
       </c>
       <c r="AC18" s="8" t="n">
         <v>24</v>
@@ -763,91 +763,91 @@
         </is>
       </c>
       <c r="B19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>8</v>
-      </c>
       <c r="G19" s="11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>10.5</v>
+        <v>6.5</v>
       </c>
       <c r="I19" s="11" t="n">
         <v>8.5</v>
       </c>
       <c r="J19" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O19" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q19" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U19" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="W19" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="X19" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y19" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC19" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD19" s="11" t="n">
         <v>10</v>
-      </c>
-      <c r="K19" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="L19" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="M19" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="N19" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="O19" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="P19" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q19" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="R19" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="S19" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="U19" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V19" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="W19" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="X19" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y19" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z19" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA19" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB19" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC19" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD19" s="11" t="n">
-        <v>8</v>
       </c>
       <c r="AE19" s="11" t="n">
         <v>2</v>
@@ -857,41 +857,39 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>ОУТС И БД кат С</t>
+          <t>ОУТС и БД</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
         <v>6</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E20" s="13" t="n">
         <v>6</v>
       </c>
       <c r="F20" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="H20" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="I20" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="13" t="n">
-        <v>4</v>
-      </c>
+      <c r="I20" s="13" t="inlineStr"/>
+      <c r="J20" s="13" t="inlineStr"/>
       <c r="K20" s="13" t="inlineStr"/>
       <c r="L20" s="13" t="inlineStr"/>
       <c r="M20" s="13" t="inlineStr"/>
       <c r="N20" s="13" t="inlineStr"/>
-      <c r="O20" s="13" t="inlineStr"/>
+      <c r="O20" s="13" t="n">
+        <v>2</v>
+      </c>
       <c r="P20" s="13" t="inlineStr"/>
       <c r="Q20" s="13" t="inlineStr"/>
       <c r="R20" s="13" t="inlineStr"/>
@@ -909,7 +907,7 @@
       <c r="AD20" s="13" t="inlineStr"/>
       <c r="AE20" s="13" t="inlineStr"/>
       <c r="AF20" s="11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -937,9 +935,7 @@
       <c r="R21" s="13" t="inlineStr"/>
       <c r="S21" s="13" t="inlineStr"/>
       <c r="T21" s="13" t="inlineStr"/>
-      <c r="U21" s="13" t="n">
-        <v>4</v>
-      </c>
+      <c r="U21" s="13" t="inlineStr"/>
       <c r="V21" s="13" t="n">
         <v>4</v>
       </c>
@@ -949,7 +945,9 @@
       <c r="X21" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="Y21" s="13" t="inlineStr"/>
+      <c r="Y21" s="13" t="n">
+        <v>4</v>
+      </c>
       <c r="Z21" s="13" t="inlineStr"/>
       <c r="AA21" s="13" t="inlineStr"/>
       <c r="AB21" s="13" t="inlineStr"/>
@@ -963,23 +961,29 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>У и ЭА кат. "С"</t>
+          <t>ПДД</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr"/>
       <c r="C22" s="13" t="inlineStr"/>
       <c r="D22" s="13" t="inlineStr"/>
       <c r="E22" s="13" t="inlineStr"/>
-      <c r="F22" s="13" t="inlineStr"/>
+      <c r="F22" s="13" t="n">
+        <v>6</v>
+      </c>
       <c r="G22" s="13" t="inlineStr"/>
       <c r="H22" s="13" t="inlineStr"/>
-      <c r="I22" s="13" t="inlineStr"/>
-      <c r="J22" s="13" t="inlineStr"/>
+      <c r="I22" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>4</v>
+      </c>
       <c r="K22" s="13" t="n">
         <v>6</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M22" s="13" t="n">
         <v>6</v>
@@ -988,54 +992,54 @@
         <v>6</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P22" s="13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q22" s="13" t="n">
         <v>4</v>
       </c>
       <c r="R22" s="13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S22" s="13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T22" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="U22" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="U22" s="13" t="inlineStr"/>
       <c r="V22" s="13" t="inlineStr"/>
       <c r="W22" s="13" t="inlineStr"/>
       <c r="X22" s="13" t="inlineStr"/>
-      <c r="Y22" s="13" t="n">
-        <v>4</v>
-      </c>
+      <c r="Y22" s="13" t="inlineStr"/>
       <c r="Z22" s="13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AA22" s="13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AB22" s="13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC22" s="13" t="n">
         <v>4</v>
       </c>
       <c r="AD22" s="13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE22" s="13" t="inlineStr"/>
       <c r="AF22" s="11" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Экзамен</t>
+          <t>ПОДД</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr"/>
@@ -1044,8 +1048,12 @@
       <c r="E23" s="13" t="inlineStr"/>
       <c r="F23" s="13" t="inlineStr"/>
       <c r="G23" s="13" t="inlineStr"/>
-      <c r="H23" s="13" t="inlineStr"/>
-      <c r="I23" s="13" t="inlineStr"/>
+      <c r="H23" s="13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I23" s="13" t="n">
+        <v>3.5</v>
+      </c>
       <c r="J23" s="13" t="inlineStr"/>
       <c r="K23" s="13" t="inlineStr"/>
       <c r="L23" s="13" t="inlineStr"/>
@@ -1067,17 +1075,102 @@
       <c r="AB23" s="13" t="inlineStr"/>
       <c r="AC23" s="13" t="inlineStr"/>
       <c r="AD23" s="13" t="inlineStr"/>
-      <c r="AE23" s="13" t="n">
+      <c r="AE23" s="13" t="inlineStr"/>
+      <c r="AF23" s="11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>УА</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr"/>
+      <c r="C24" s="13" t="inlineStr"/>
+      <c r="D24" s="13" t="inlineStr"/>
+      <c r="E24" s="13" t="inlineStr"/>
+      <c r="F24" s="13" t="inlineStr"/>
+      <c r="G24" s="13" t="inlineStr"/>
+      <c r="H24" s="13" t="inlineStr"/>
+      <c r="I24" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="13" t="inlineStr"/>
+      <c r="K24" s="13" t="inlineStr"/>
+      <c r="L24" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" s="13" t="inlineStr"/>
+      <c r="N24" s="13" t="inlineStr"/>
+      <c r="O24" s="13" t="inlineStr"/>
+      <c r="P24" s="13" t="inlineStr"/>
+      <c r="Q24" s="13" t="inlineStr"/>
+      <c r="R24" s="13" t="inlineStr"/>
+      <c r="S24" s="13" t="inlineStr"/>
+      <c r="T24" s="13" t="inlineStr"/>
+      <c r="U24" s="13" t="inlineStr"/>
+      <c r="V24" s="13" t="inlineStr"/>
+      <c r="W24" s="13" t="inlineStr"/>
+      <c r="X24" s="13" t="inlineStr"/>
+      <c r="Y24" s="13" t="inlineStr"/>
+      <c r="Z24" s="13" t="inlineStr"/>
+      <c r="AA24" s="13" t="inlineStr"/>
+      <c r="AB24" s="13" t="inlineStr"/>
+      <c r="AC24" s="13" t="inlineStr"/>
+      <c r="AD24" s="13" t="inlineStr"/>
+      <c r="AE24" s="13" t="inlineStr"/>
+      <c r="AF24" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Экзамен</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr"/>
+      <c r="C25" s="13" t="inlineStr"/>
+      <c r="D25" s="13" t="inlineStr"/>
+      <c r="E25" s="13" t="inlineStr"/>
+      <c r="F25" s="13" t="inlineStr"/>
+      <c r="G25" s="13" t="inlineStr"/>
+      <c r="H25" s="13" t="inlineStr"/>
+      <c r="I25" s="13" t="inlineStr"/>
+      <c r="J25" s="13" t="inlineStr"/>
+      <c r="K25" s="13" t="inlineStr"/>
+      <c r="L25" s="13" t="inlineStr"/>
+      <c r="M25" s="13" t="inlineStr"/>
+      <c r="N25" s="13" t="inlineStr"/>
+      <c r="O25" s="13" t="inlineStr"/>
+      <c r="P25" s="13" t="inlineStr"/>
+      <c r="Q25" s="13" t="inlineStr"/>
+      <c r="R25" s="13" t="inlineStr"/>
+      <c r="S25" s="13" t="inlineStr"/>
+      <c r="T25" s="13" t="inlineStr"/>
+      <c r="U25" s="13" t="inlineStr"/>
+      <c r="V25" s="13" t="inlineStr"/>
+      <c r="W25" s="13" t="inlineStr"/>
+      <c r="X25" s="13" t="inlineStr"/>
+      <c r="Y25" s="13" t="inlineStr"/>
+      <c r="Z25" s="13" t="inlineStr"/>
+      <c r="AA25" s="13" t="inlineStr"/>
+      <c r="AB25" s="13" t="inlineStr"/>
+      <c r="AC25" s="13" t="inlineStr"/>
+      <c r="AD25" s="13" t="inlineStr"/>
+      <c r="AE25" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="AF23" s="11" t="n">
+      <c r="AF25" s="11" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="B12:AF12"/>
-    <mergeCell ref="J17:T17"/>
+    <mergeCell ref="V17:AD17"/>
+    <mergeCell ref="K17:U17"/>
     <mergeCell ref="T1:AF1"/>
     <mergeCell ref="Y4:AF4"/>
     <mergeCell ref="B15:AF15"/>
@@ -1087,11 +1180,10 @@
     <mergeCell ref="A8:AF8"/>
     <mergeCell ref="A6:AF6"/>
     <mergeCell ref="T3:AF3"/>
+    <mergeCell ref="B17:J17"/>
     <mergeCell ref="B14:AF14"/>
-    <mergeCell ref="U17:AD17"/>
     <mergeCell ref="B13:AF13"/>
     <mergeCell ref="T2:AF2"/>
-    <mergeCell ref="B17:I17"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
